--- a/application/tests/Fixtures/Ndi/invalid_decimal.xlsx
+++ b/application/tests/Fixtures/Ndi/invalid_decimal.xlsx
@@ -522,7 +522,7 @@
       </x:c>
       <x:c r="AF2" s="9"/>
       <x:c r="AG2" s="9" t="str">
-        <x:v>https://example.invalid/TEST-TIRE-002.png</x:v>
+        <x:v>https://example.invalid/Imagev2.aspx?id=22222222-2222-4222-8222-222222222222</x:v>
       </x:c>
       <x:c r="AH2" s="9"/>
     </x:row>
